--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A20FA6D-7810-A947-93C3-BBFD31C62842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDDCA280-7F5D-A942-ADD8-21D602024031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="59">
   <si>
     <t>week</t>
   </si>
@@ -204,6 +204,12 @@
   </si>
   <si>
     <t>6-exams/practice/midterm1-practice.qmd</t>
+  </si>
+  <si>
+    <t>2-slides/04.2-analyzing-a-factorial.qmd</t>
+  </si>
+  <si>
+    <t>1-prep/04.2-prep.qmd</t>
   </si>
 </sst>
 </file>
@@ -781,8 +787,12 @@
       <c r="D8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
+      <c r="E8" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
     </row>

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDDCA280-7F5D-A942-ADD8-21D602024031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A934EDBF-F90C-894C-ACE1-6536C51899E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="61">
   <si>
     <t>week</t>
   </si>
@@ -210,6 +210,12 @@
   </si>
   <si>
     <t>1-prep/04.2-prep.qmd</t>
+  </si>
+  <si>
+    <t>3-activities/instructions/04.2-activity-analyze-factorials.qmd</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1zYPjkIp9R6vygh8kYLwj0hp7THuQf9wUlZYz4ONd6hA/edit?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -793,8 +799,12 @@
       <c r="F8" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
+      <c r="G8" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1">

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A934EDBF-F90C-894C-ACE1-6536C51899E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3DE25C6-CB13-0246-A481-C125623928F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="63">
   <si>
     <t>week</t>
   </si>
@@ -216,6 +216,12 @@
   </si>
   <si>
     <t>https://docs.google.com/presentation/d/1zYPjkIp9R6vygh8kYLwj0hp7THuQf9wUlZYz4ONd6hA/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>1-prep/04.3-prep.qmd</t>
+  </si>
+  <si>
+    <t>2-slides/04.3-higher-order-interactions.qmd</t>
   </si>
 </sst>
 </file>
@@ -841,8 +847,12 @@
       <c r="D10" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
+      <c r="E10" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>62</v>
+      </c>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
     </row>

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3DE25C6-CB13-0246-A481-C125623928F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DFF45BE-96CD-F84E-A59A-E4CA7E5016CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="66">
   <si>
     <t>week</t>
   </si>
@@ -222,6 +222,15 @@
   </si>
   <si>
     <t>2-slides/04.3-higher-order-interactions.qmd</t>
+  </si>
+  <si>
+    <t>2-slides/05.1-design-analyze-rcbd.qmd</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1XBsJ83o-3HaQZP37dWNqCLQfHSNT0AcTkT7Hh_w3IJc/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>1-prep/05.1-prep.qmd</t>
   </si>
 </sst>
 </file>
@@ -853,7 +862,9 @@
       <c r="F10" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G10" s="7"/>
+      <c r="G10" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="H10" s="7"/>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -870,8 +881,12 @@
       <c r="D11" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
+      <c r="E11" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>63</v>
+      </c>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DFF45BE-96CD-F84E-A59A-E4CA7E5016CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71208EEA-E846-3740-B147-63E604F858D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="67">
   <si>
     <t>week</t>
   </si>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t>1-prep/05.1-prep.qmd</t>
+  </si>
+  <si>
+    <t>3-activities/instructions/05.1-activity-reducing-variability-with-blocking.qmd</t>
   </si>
 </sst>
 </file>
@@ -888,7 +891,9 @@
         <v>63</v>
       </c>
       <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
+      <c r="H11" s="7" t="s">
+        <v>66</v>
+      </c>
       <c r="I11" s="7"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71208EEA-E846-3740-B147-63E604F858D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA80B48-5378-3247-AA48-B66A5254403C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="68">
   <si>
     <t>week</t>
   </si>
@@ -234,6 +234,9 @@
   </si>
   <si>
     <t>3-activities/instructions/05.1-activity-reducing-variability-with-blocking.qmd</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1fFmKO692bu00JH5NpM9o9eT0IwXXy2ld8n5d-EjfaqA/edit?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -890,7 +893,9 @@
       <c r="F11" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="G11" s="7"/>
+      <c r="G11" s="7" t="s">
+        <v>67</v>
+      </c>
       <c r="H11" s="7" t="s">
         <v>66</v>
       </c>

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA80B48-5378-3247-AA48-B66A5254403C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B7F247-BB86-7A45-BFF3-2BBA545ECBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="69">
   <si>
     <t>week</t>
   </si>
@@ -237,6 +237,9 @@
   </si>
   <si>
     <t>https://docs.google.com/presentation/d/1fFmKO692bu00JH5NpM9o9eT0IwXXy2ld8n5d-EjfaqA/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>2-slides/05.2-factorial-in-rcbd.html</t>
   </si>
 </sst>
 </file>
@@ -915,8 +918,12 @@
       <c r="D12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+      <c r="E12" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>68</v>
+      </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
     </row>

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B7F247-BB86-7A45-BFF3-2BBA545ECBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFF172D2-8AB2-A647-BFCE-6F66F769633E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="72">
   <si>
     <t>week</t>
   </si>
@@ -239,7 +239,16 @@
     <t>https://docs.google.com/presentation/d/1fFmKO692bu00JH5NpM9o9eT0IwXXy2ld8n5d-EjfaqA/edit?usp=sharing</t>
   </si>
   <si>
-    <t>2-slides/05.2-factorial-in-rcbd.html</t>
+    <t>1-prep/05.2-prep.qmd</t>
+  </si>
+  <si>
+    <t>1-prep/06.1-prep.qmd</t>
+  </si>
+  <si>
+    <t>2-slides/05.2-factorial-in-rcbd.qmd</t>
+  </si>
+  <si>
+    <t>2-slides/06.1-random-effects.qmd</t>
   </si>
 </sst>
 </file>
@@ -919,10 +928,10 @@
         <v>19</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
@@ -941,8 +950,12 @@
       <c r="D13" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
+      <c r="E13" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1">

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFF172D2-8AB2-A647-BFCE-6F66F769633E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCABDDA0-7575-244D-AB87-7E0399A2D56E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="73">
   <si>
     <t>week</t>
   </si>
@@ -249,6 +249,9 @@
   </si>
   <si>
     <t>2-slides/06.1-random-effects.qmd</t>
+  </si>
+  <si>
+    <t>4-labs/lab3-factorial.qmd</t>
   </si>
 </sst>
 </file>
@@ -935,6 +938,9 @@
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
+      <c r="I12" s="7" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="1">

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCABDDA0-7575-244D-AB87-7E0399A2D56E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{268824D8-F468-364D-9167-5DB74170B3B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4080" yWindow="600" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="75">
   <si>
     <t>week</t>
   </si>
@@ -252,6 +252,12 @@
   </si>
   <si>
     <t>4-labs/lab3-factorial.qmd</t>
+  </si>
+  <si>
+    <t>3-activities/instructions/05.2-activity-factorial-blocking.qmd</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1Yk6pdE3H0PCLXP9f2IbbZXX7QI6KPaFCY-U9Njen41g/edit?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -936,8 +942,12 @@
       <c r="F12" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
+      <c r="G12" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>73</v>
+      </c>
       <c r="I12" s="7" t="s">
         <v>72</v>
       </c>

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{268824D8-F468-364D-9167-5DB74170B3B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4080" yWindow="600" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{268824D8-F468-364D-9167-5DB74170B3B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BBC72CC-9F4C-7E4D-A258-32E07F7B82D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="76">
   <si>
     <t>week</t>
   </si>
@@ -258,6 +258,9 @@
   </si>
   <si>
     <t>https://docs.google.com/presentation/d/1Yk6pdE3H0PCLXP9f2IbbZXX7QI6KPaFCY-U9Njen41g/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>3-activities/instructions/06.1-activity-color-interference.qmd</t>
   </si>
 </sst>
 </file>
@@ -355,17 +358,17 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
-      </top>
-      <bottom/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -377,22 +380,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -662,7 +669,7 @@
       <c r="C2" s="6">
         <v>46259</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E2" s="7" t="s">
@@ -689,7 +696,7 @@
         <f>C2+2</f>
         <v>46261</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -719,7 +726,7 @@
         <f>C2+7</f>
         <v>46266</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="11" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="7" t="s">
@@ -746,7 +753,7 @@
         <f>C4+2</f>
         <v>46268</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="11" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="7" t="s">
@@ -774,7 +781,7 @@
         <f>C4+7</f>
         <v>46273</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="12" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="7" t="s">
@@ -804,7 +811,7 @@
         <f>C6+2</f>
         <v>46275</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="12" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="7" t="s">
@@ -832,7 +839,7 @@
         <f>C6+7</f>
         <v>46280</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="12" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="7" t="s">
@@ -849,24 +856,24 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="1">
+      <c r="A9" s="13">
         <v>4</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="14">
         <f>C8+2</f>
         <v>46282</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
       <c r="I9" s="7"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -880,7 +887,7 @@
         <f>C8+7</f>
         <v>46287</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="12" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="7" t="s">
@@ -905,7 +912,7 @@
         <f>C10+2</f>
         <v>46289</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="11" t="s">
         <v>19</v>
       </c>
       <c r="E11" s="7" t="s">
@@ -933,7 +940,7 @@
         <f>C10+7</f>
         <v>46294</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="11" t="s">
         <v>19</v>
       </c>
       <c r="E12" s="7" t="s">
@@ -963,7 +970,7 @@
         <f>C12+2</f>
         <v>46296</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="11" t="s">
         <v>20</v>
       </c>
       <c r="E13" s="7" t="s">
@@ -971,6 +978,9 @@
       </c>
       <c r="F13" s="7" t="s">
         <v>71</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -984,7 +994,7 @@
         <f>C12+7</f>
         <v>46301</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="11" t="s">
         <v>20</v>
       </c>
       <c r="E14" s="7"/>
@@ -1003,7 +1013,7 @@
         <f>C14+2</f>
         <v>46303</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="11" t="s">
         <v>21</v>
       </c>
       <c r="E15" s="7"/>
@@ -1022,7 +1032,7 @@
         <f>C14+7</f>
         <v>46308</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="11" t="s">
         <v>21</v>
       </c>
       <c r="E16" s="7"/>
@@ -1041,7 +1051,7 @@
         <f>C16+2</f>
         <v>46310</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="11" t="s">
         <v>22</v>
       </c>
       <c r="E17" s="7"/>
@@ -1051,19 +1061,22 @@
       <c r="I17" s="7"/>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="1">
+      <c r="A18" s="13">
         <v>9</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="14">
         <f>C16+7</f>
         <v>46315</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="15" t="s">
         <v>7</v>
       </c>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
     </row>
     <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
@@ -1076,7 +1089,7 @@
         <f>C18+2</f>
         <v>46317</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="11" t="s">
         <v>23</v>
       </c>
       <c r="E19" s="7"/>
@@ -1095,7 +1108,7 @@
         <f>C19+5</f>
         <v>46322</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="11" t="s">
         <v>23</v>
       </c>
       <c r="E20" s="7"/>
@@ -1114,7 +1127,7 @@
         <f>C20+2</f>
         <v>46324</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="7"/>
@@ -1130,7 +1143,7 @@
         <f>C21+5</f>
         <v>46329</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="3"/>
@@ -1147,7 +1160,7 @@
         <f>C22+2</f>
         <v>46331</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="3"/>
@@ -1163,7 +1176,7 @@
         <f>C23+5</f>
         <v>46336</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="9" t="s">
         <v>27</v>
       </c>
       <c r="G24" s="3"/>
@@ -1179,7 +1192,7 @@
         <f>C24+2</f>
         <v>46338</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="9" t="s">
         <v>27</v>
       </c>
       <c r="G25" s="3"/>
@@ -1195,25 +1208,28 @@
         <f>C25+5</f>
         <v>46343</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D26" s="9" t="s">
         <v>27</v>
       </c>
       <c r="G26" s="3"/>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="1">
+      <c r="A27" s="13">
         <v>13</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="14">
         <f>C26+2</f>
         <v>46345</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="18" t="s">
         <v>24</v>
       </c>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
       <c r="I27" s="1"/>
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BBC72CC-9F4C-7E4D-A258-32E07F7B82D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D320D547-6713-7448-A1AD-6817F6777E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="79">
   <si>
     <t>week</t>
   </si>
@@ -261,6 +261,15 @@
   </si>
   <si>
     <t>3-activities/instructions/06.1-activity-color-interference.qmd</t>
+  </si>
+  <si>
+    <t>1-prep/06.2-prep.qmd</t>
+  </si>
+  <si>
+    <t>2-slides/06.2-subsampling-with-random-effects.qmd</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1H1vy8YhR_CdbpuC7a4-f0j4mVrYejdXw-JYUVMPhCfY/</t>
   </si>
 </sst>
 </file>
@@ -368,7 +377,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -386,10 +395,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -669,7 +675,7 @@
       <c r="C2" s="6">
         <v>46259</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="8" t="s">
         <v>15</v>
       </c>
       <c r="E2" s="7" t="s">
@@ -696,7 +702,7 @@
         <f>C2+2</f>
         <v>46261</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="8" t="s">
         <v>15</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -726,7 +732,7 @@
         <f>C2+7</f>
         <v>46266</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="7" t="s">
@@ -753,7 +759,7 @@
         <f>C4+2</f>
         <v>46268</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="7" t="s">
@@ -781,7 +787,7 @@
         <f>C4+7</f>
         <v>46273</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="7" t="s">
@@ -811,7 +817,7 @@
         <f>C6+2</f>
         <v>46275</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="11" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="7" t="s">
@@ -839,7 +845,7 @@
         <f>C6+7</f>
         <v>46280</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="11" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="7" t="s">
@@ -856,24 +862,24 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="13">
+      <c r="A9" s="12">
         <v>4</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="13">
         <f>C8+2</f>
         <v>46282</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
       <c r="I9" s="7"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -887,7 +893,7 @@
         <f>C8+7</f>
         <v>46287</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="11" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="7" t="s">
@@ -912,7 +918,7 @@
         <f>C10+2</f>
         <v>46289</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E11" s="7" t="s">
@@ -940,7 +946,7 @@
         <f>C10+7</f>
         <v>46294</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E12" s="7" t="s">
@@ -970,7 +976,7 @@
         <f>C12+2</f>
         <v>46296</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="8" t="s">
         <v>20</v>
       </c>
       <c r="E13" s="7" t="s">
@@ -978,6 +984,9 @@
       </c>
       <c r="F13" s="7" t="s">
         <v>71</v>
+      </c>
+      <c r="G13" t="s">
+        <v>78</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>75</v>
@@ -994,11 +1003,15 @@
         <f>C12+7</f>
         <v>46301</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
+      <c r="E14" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
     </row>
@@ -1013,7 +1026,7 @@
         <f>C14+2</f>
         <v>46303</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="8" t="s">
         <v>21</v>
       </c>
       <c r="E15" s="7"/>
@@ -1032,7 +1045,7 @@
         <f>C14+7</f>
         <v>46308</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="8" t="s">
         <v>21</v>
       </c>
       <c r="E16" s="7"/>
@@ -1051,7 +1064,7 @@
         <f>C16+2</f>
         <v>46310</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="8" t="s">
         <v>22</v>
       </c>
       <c r="E17" s="7"/>
@@ -1061,22 +1074,22 @@
       <c r="I17" s="7"/>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="13">
+      <c r="A18" s="12">
         <v>9</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="13">
         <f>C16+7</f>
         <v>46315</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
     </row>
     <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
@@ -1089,7 +1102,7 @@
         <f>C18+2</f>
         <v>46317</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="8" t="s">
         <v>23</v>
       </c>
       <c r="E19" s="7"/>
@@ -1108,7 +1121,7 @@
         <f>C19+5</f>
         <v>46322</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="8" t="s">
         <v>23</v>
       </c>
       <c r="E20" s="7"/>
@@ -1214,22 +1227,22 @@
       <c r="G26" s="3"/>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="13">
+      <c r="A27" s="12">
         <v>13</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13">
         <f>C26+2</f>
         <v>46345</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="D27" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
       <c r="I27" s="1"/>
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D320D547-6713-7448-A1AD-6817F6777E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704514CC-FB1D-B44F-A826-B0A4E6E95325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="81">
   <si>
     <t>week</t>
   </si>
@@ -270,6 +270,12 @@
   </si>
   <si>
     <t>https://docs.google.com/presentation/d/1H1vy8YhR_CdbpuC7a4-f0j4mVrYejdXw-JYUVMPhCfY/</t>
+  </si>
+  <si>
+    <t>1-prep/07.1-prep.qmd</t>
+  </si>
+  <si>
+    <t>2-slides/07.1-more-designs.qmd</t>
   </si>
 </sst>
 </file>
@@ -1029,8 +1035,12 @@
       <c r="D15" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="E15" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>80</v>
+      </c>
       <c r="G15" s="7"/>
       <c r="I15" s="7"/>
     </row>

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704514CC-FB1D-B44F-A826-B0A4E6E95325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8EB843-2D72-144E-B784-7B69382DC491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="83">
   <si>
     <t>week</t>
   </si>
@@ -276,6 +276,12 @@
   </si>
   <si>
     <t>2-slides/07.1-more-designs.qmd</t>
+  </si>
+  <si>
+    <t>3-activities/instructions/06.2-activity-subsampling.qmd</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1dBzGEExrhUTM1T7zLMOr3MCZeZWTmTtMcCfUPAc3ogY/edit?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -1018,8 +1024,12 @@
       <c r="F14" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
+      <c r="G14" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="1">

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8EB843-2D72-144E-B784-7B69382DC491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9009F3C6-770C-CD4A-931B-73DF23E82D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="84">
   <si>
     <t>week</t>
   </si>
@@ -282,6 +282,9 @@
   </si>
   <si>
     <t>https://docs.google.com/presentation/d/1dBzGEExrhUTM1T7zLMOr3MCZeZWTmTtMcCfUPAc3ogY/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>3-activities/instructions/07.1-activity-latin-squares.qmd</t>
   </si>
 </sst>
 </file>
@@ -1052,6 +1055,9 @@
         <v>80</v>
       </c>
       <c r="G15" s="7"/>
+      <c r="H15" s="7" t="s">
+        <v>83</v>
+      </c>
       <c r="I15" s="7"/>
     </row>
     <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9009F3C6-770C-CD4A-931B-73DF23E82D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{249AC96A-79CC-D349-B25E-05005240CE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="85">
   <si>
     <t>week</t>
   </si>
@@ -285,6 +285,9 @@
   </si>
   <si>
     <t>3-activities/instructions/07.1-activity-latin-squares.qmd</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1VoWvuFMsNbVO5FPdb5n3ckUyS90PdOLojxTTcUeTTIw/edit?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -1054,7 +1057,9 @@
       <c r="F15" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="G15" s="7"/>
+      <c r="G15" s="7" t="s">
+        <v>84</v>
+      </c>
       <c r="H15" s="7" t="s">
         <v>83</v>
       </c>

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{249AC96A-79CC-D349-B25E-05005240CE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBB89111-E28D-9C4D-8D73-2D2ADC73ACFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="87">
   <si>
     <t>week</t>
   </si>
@@ -288,6 +288,12 @@
   </si>
   <si>
     <t>https://docs.google.com/presentation/d/1VoWvuFMsNbVO5FPdb5n3ckUyS90PdOLojxTTcUeTTIw/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>2-slides/07.2-nonparametric.qmd</t>
+  </si>
+  <si>
+    <t>1-prep/07.2-prep.qmd</t>
   </si>
 </sst>
 </file>
@@ -1079,8 +1085,12 @@
       <c r="D16" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
+      <c r="E16" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>85</v>
+      </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
     </row>

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBB89111-E28D-9C4D-8D73-2D2ADC73ACFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01922F8D-B783-A940-94C0-CE8249E6888A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="90">
   <si>
     <t>week</t>
   </si>
@@ -294,6 +294,15 @@
   </si>
   <si>
     <t>1-prep/07.2-prep.qmd</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1lye95sCgZcemNT8SeQ7YRkFnMKVEA4rIxcoCy5H_MrY/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>1-prep/08.1-prep.qmd</t>
+  </si>
+  <si>
+    <t>2-slides/08.1-causalinference.qmd</t>
   </si>
 </sst>
 </file>
@@ -1091,7 +1100,9 @@
       <c r="F16" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="G16" s="7"/>
+      <c r="G16" s="7" t="s">
+        <v>87</v>
+      </c>
       <c r="H16" s="7"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1108,8 +1119,12 @@
       <c r="D17" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
+      <c r="E17" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01922F8D-B783-A940-94C0-CE8249E6888A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A2D00B-010D-4042-9684-68CA41700810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>week</t>
   </si>
@@ -303,6 +303,12 @@
   </si>
   <si>
     <t>2-slides/08.1-causalinference.qmd</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1dwsxpz7zjO8hV39ldAjQUHM0o3jevr8ZWj0tQ02cIg0/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>3-activities/instructions/08.1-causal-inference.qmd</t>
   </si>
 </sst>
 </file>
@@ -1125,8 +1131,12 @@
       <c r="F17" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
+      <c r="G17" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="I17" s="7"/>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A2D00B-010D-4042-9684-68CA41700810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E42E2F45-9D40-7345-9128-C2403F8EE967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -308,7 +308,7 @@
     <t>https://docs.google.com/presentation/d/1dwsxpz7zjO8hV39ldAjQUHM0o3jevr8ZWj0tQ02cIg0/edit?usp=sharing</t>
   </si>
   <si>
-    <t>3-activities/instructions/08.1-causal-inference.qmd</t>
+    <t>3-activities/instructions/08.1-activity-causal-inference.qmd</t>
   </si>
 </sst>
 </file>

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E42E2F45-9D40-7345-9128-C2403F8EE967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C1DEB2-B91E-3D46-A1CA-9F3A288F94B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -302,13 +302,13 @@
     <t>1-prep/08.1-prep.qmd</t>
   </si>
   <si>
-    <t>2-slides/08.1-causalinference.qmd</t>
-  </si>
-  <si>
     <t>https://docs.google.com/presentation/d/1dwsxpz7zjO8hV39ldAjQUHM0o3jevr8ZWj0tQ02cIg0/edit?usp=sharing</t>
   </si>
   <si>
     <t>3-activities/instructions/08.1-activity-causal-inference.qmd</t>
+  </si>
+  <si>
+    <t>2-slides/08.1-causal-inference.qmd</t>
   </si>
 </sst>
 </file>
@@ -1129,13 +1129,13 @@
         <v>88</v>
       </c>
       <c r="F17" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G17" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="H17" s="7" t="s">
         <v>90</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>91</v>
       </c>
       <c r="I17" s="7"/>
     </row>

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C1DEB2-B91E-3D46-A1CA-9F3A288F94B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42623CD8-22DC-5A48-B22F-28BE05809CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="93">
   <si>
     <t>week</t>
   </si>
@@ -107,18 +107,9 @@
     <t>Mod 9: Observational Studies</t>
   </si>
   <si>
-    <t>Mod 12: Survey Weights</t>
-  </si>
-  <si>
     <t>Mod 13: Putting it all Together!</t>
   </si>
   <si>
-    <t>Mod 10: Writing Survey Instruments</t>
-  </si>
-  <si>
-    <t>Mod 11: Survey Sampling</t>
-  </si>
-  <si>
     <t>class_slides</t>
   </si>
   <si>
@@ -309,6 +300,18 @@
   </si>
   <si>
     <t>2-slides/08.1-causal-inference.qmd</t>
+  </si>
+  <si>
+    <t>6-exams/practice/midterm2-practice.qmd</t>
+  </si>
+  <si>
+    <t>Mod 10: Survey Sampling</t>
+  </si>
+  <si>
+    <t>Mod 11: Survey Weights</t>
+  </si>
+  <si>
+    <t>Mod 12: Writing Survey Instruments</t>
   </si>
 </sst>
 </file>
@@ -416,7 +419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -444,7 +447,10 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -692,10 +698,10 @@
         <v>14</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
@@ -718,16 +724,16 @@
         <v>15</v>
       </c>
       <c r="E2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" t="s">
-        <v>35</v>
-      </c>
       <c r="H2" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -745,19 +751,19 @@
         <v>15</v>
       </c>
       <c r="E3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>36</v>
-      </c>
       <c r="I3" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -775,16 +781,16 @@
         <v>16</v>
       </c>
       <c r="E4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" t="s">
-        <v>43</v>
-      </c>
       <c r="H4" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -802,16 +808,16 @@
         <v>16</v>
       </c>
       <c r="E5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>42</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>45</v>
       </c>
       <c r="I5" s="7"/>
     </row>
@@ -830,19 +836,19 @@
         <v>17</v>
       </c>
       <c r="E6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="I6" s="7" t="s">
         <v>48</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -860,16 +866,16 @@
         <v>18</v>
       </c>
       <c r="E7" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>55</v>
-      </c>
       <c r="H7" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I7" s="7"/>
     </row>
@@ -888,16 +894,16 @@
         <v>18</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>60</v>
-      </c>
       <c r="H8" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -915,7 +921,7 @@
         <v>6</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
@@ -936,13 +942,13 @@
         <v>18</v>
       </c>
       <c r="E10" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>61</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>64</v>
       </c>
       <c r="H10" s="7"/>
     </row>
@@ -961,16 +967,16 @@
         <v>19</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F11" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" s="7" t="s">
         <v>63</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>66</v>
       </c>
       <c r="I11" s="7"/>
     </row>
@@ -989,19 +995,19 @@
         <v>19</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F12" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="G12" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>73</v>
-      </c>
       <c r="I12" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1019,16 +1025,16 @@
         <v>20</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G13" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1046,16 +1052,16 @@
         <v>20</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1073,16 +1079,16 @@
         <v>21</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F15" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H15" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="I15" s="7"/>
     </row>
@@ -1101,13 +1107,13 @@
         <v>21</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H16" s="7"/>
     </row>
@@ -1126,16 +1132,16 @@
         <v>22</v>
       </c>
       <c r="E17" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>91</v>
-      </c>
       <c r="G17" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I17" s="7"/>
     </row>
@@ -1153,7 +1159,9 @@
       <c r="D18" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="16"/>
+      <c r="E18" s="15" t="s">
+        <v>89</v>
+      </c>
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
     </row>
@@ -1206,8 +1214,8 @@
         <f>C20+2</f>
         <v>46324</v>
       </c>
-      <c r="D21" s="10" t="s">
-        <v>26</v>
+      <c r="D21" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="G21" s="7"/>
     </row>
@@ -1222,8 +1230,8 @@
         <f>C21+5</f>
         <v>46329</v>
       </c>
-      <c r="D22" s="10" t="s">
-        <v>26</v>
+      <c r="D22" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="1"/>
@@ -1239,8 +1247,8 @@
         <f>C22+2</f>
         <v>46331</v>
       </c>
-      <c r="D23" s="10" t="s">
-        <v>26</v>
+      <c r="D23" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="G23" s="3"/>
     </row>
@@ -1255,8 +1263,8 @@
         <f>C23+5</f>
         <v>46336</v>
       </c>
-      <c r="D24" s="9" t="s">
-        <v>27</v>
+      <c r="D24" s="18" t="s">
+        <v>91</v>
       </c>
       <c r="G24" s="3"/>
     </row>
@@ -1271,8 +1279,8 @@
         <f>C24+2</f>
         <v>46338</v>
       </c>
-      <c r="D25" s="9" t="s">
-        <v>27</v>
+      <c r="D25" s="10" t="s">
+        <v>92</v>
       </c>
       <c r="G25" s="3"/>
     </row>
@@ -1287,8 +1295,8 @@
         <f>C25+5</f>
         <v>46343</v>
       </c>
-      <c r="D26" s="9" t="s">
-        <v>27</v>
+      <c r="D26" s="10" t="s">
+        <v>92</v>
       </c>
       <c r="G26" s="3"/>
     </row>
@@ -1304,7 +1312,7 @@
         <v>46345</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="E27" s="16"/>
       <c r="F27" s="16"/>
@@ -1352,7 +1360,7 @@
         <v>46357</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G30" s="5"/>
       <c r="I30" s="1"/>
@@ -1369,7 +1377,7 @@
         <v>46359</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G31" s="4"/>
       <c r="I31" s="1"/>
@@ -1386,7 +1394,7 @@
         <v>46364</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I32" s="1"/>
     </row>

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42623CD8-22DC-5A48-B22F-28BE05809CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D414397C-31EE-EF44-A8EA-5A08F9368DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="95">
   <si>
     <t>week</t>
   </si>
@@ -312,6 +312,12 @@
   </si>
   <si>
     <t>Mod 12: Writing Survey Instruments</t>
+  </si>
+  <si>
+    <t>3-activities/instructions/09.1-activity-polls.qmd</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1M0auJ1RQRnhmnCwaROR4BCmirVWO-fHJ-HlmCq2LNEQ/edit?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -1181,7 +1187,12 @@
       </c>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
+      <c r="G19" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>93</v>
+      </c>
       <c r="I19" s="7"/>
     </row>
     <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D414397C-31EE-EF44-A8EA-5A08F9368DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA8DB54-7245-4445-AA0A-26AB6891A031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="97">
   <si>
     <t>week</t>
   </si>
@@ -318,6 +318,12 @@
   </si>
   <si>
     <t>https://docs.google.com/presentation/d/1M0auJ1RQRnhmnCwaROR4BCmirVWO-fHJ-HlmCq2LNEQ/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>1-prep/09.2-prep.qmd</t>
+  </si>
+  <si>
+    <t>2-slides/09.2-obs-studies.qmd</t>
   </si>
 </sst>
 </file>
@@ -1209,8 +1215,12 @@
       <c r="D20" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
+      <c r="E20" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>96</v>
+      </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA8DB54-7245-4445-AA0A-26AB6891A031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE928F4-F213-0248-935F-2775B929A61C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="99">
   <si>
     <t>week</t>
   </si>
@@ -324,6 +324,12 @@
   </si>
   <si>
     <t>2-slides/09.2-obs-studies.qmd</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1B1mkKidqdrMzCSDddp2OMTMrhFM8gXgPGFVkDyQOMq0/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>3-activities/instructions/09.2-activity-administrative-data.qmd</t>
   </si>
 </sst>
 </file>
@@ -1221,8 +1227,12 @@
       <c r="F20" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
+      <c r="G20" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="1">

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE928F4-F213-0248-935F-2775B929A61C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B2839D-23FA-634B-B0C6-5A5F3AFC1BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="101">
   <si>
     <t>week</t>
   </si>
@@ -330,6 +330,12 @@
   </si>
   <si>
     <t>3-activities/instructions/09.2-activity-administrative-data.qmd</t>
+  </si>
+  <si>
+    <t>1-prep/10.1-prep.qmd</t>
+  </si>
+  <si>
+    <t>2-slides/10.1-survey-sampling.qmd</t>
   </si>
 </sst>
 </file>
@@ -1248,6 +1254,12 @@
       <c r="D21" s="9" t="s">
         <v>90</v>
       </c>
+      <c r="E21" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>100</v>
+      </c>
       <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B2839D-23FA-634B-B0C6-5A5F3AFC1BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78CFAD7C-6826-CF4A-A292-A02F9570A4A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="102">
   <si>
     <t>week</t>
   </si>
@@ -336,6 +336,9 @@
   </si>
   <si>
     <t>2-slides/10.1-survey-sampling.qmd</t>
+  </si>
+  <si>
+    <t>4-labs/lab4-sampling.qmd</t>
   </si>
 </sst>
 </file>
@@ -1261,6 +1264,9 @@
         <v>100</v>
       </c>
       <c r="G21" s="7"/>
+      <c r="I21" s="7" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="1">

--- a/stat-3540-f26-schedule.xlsx
+++ b/stat-3540-f26-schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78CFAD7C-6826-CF4A-A292-A02F9570A4A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25227419-2485-EC4E-9AEB-D62D063642CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="104">
   <si>
     <t>week</t>
   </si>
@@ -339,6 +339,12 @@
   </si>
   <si>
     <t>4-labs/lab4-sampling.qmd</t>
+  </si>
+  <si>
+    <t>3-activities/instructions/10.1-activity-simple-random-sampling.qmd</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1FUcEzNZnKvTXjP7xp8pCFU7nVB5fRm4gn1UtCabmAkg/edit?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -1263,7 +1269,12 @@
       <c r="F21" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="G21" s="7"/>
+      <c r="G21" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>102</v>
+      </c>
       <c r="I21" s="7" t="s">
         <v>101</v>
       </c>
